--- a/99-产品原型prototype/政策管理/政策管理导入模板_四档公斤段.xlsx
+++ b/99-产品原型prototype/政策管理/政策管理导入模板_四档公斤段.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="政策导入模板" sheetId="1" r:id="R4608ed29688c4a8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R509e4e1a85144a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="枚举值" sheetId="3" r:id="R801f7612098e42de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="政策导入模板" sheetId="1" r:id="Ra375fc74e4bb462e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" r:id="R8607231ba4a841b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="枚举值" sheetId="3" r:id="R3d14b95db0674ecb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -138,160 +138,10 @@
     <x:t xml:space="preserve">月</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">你好</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">佰川物流S站</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">毕节金沙站</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">网点返利政策导入填写说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">日期字段使用日期校验；产品类型、货物类型和公斤段使用下拉列表，可选择全部、单个或预组合的多个值；考核周期只能单选。</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">字段名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">是否必填</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">填写格式</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">填写规则</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">系统拆分规则示例</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">是</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">日期选择</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择或输入政策生效起始日期，不得晚于结束日期</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">输入项目</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">示例</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">说明</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择或输入政策生效结束日期；允许跨月并由系统按自然月拆分</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">日期范围</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2026-09-15 至 2026-10-31</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">跨2个自然月</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">文本</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">填写系统中的标准网点名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择2个产品类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">填写分拨或营运区名称；营运区覆盖导入时快照内的分拨</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择2个货物类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">列表选择</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">下拉可选择全部、单个或预组合的多个产品类型</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择3个公斤段</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">下拉可选择全部、单个或预组合的多个货物类型：轻泡、重泡、重货</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">拆分结果</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2 × 2 × 2 × 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">导入系统后形成24条月度配置</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">仅可选择0kg-100kg、100kg-300kg、300kg-800kg、800kg-1500kg；支持全部、单选和预组合多选</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">单选列表</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">只能单选周或月</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">导入校验</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数值（kg）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">大于或等于0</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1. 日期、网点、流向和必填字段不能为空</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">数值（元/kg）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">大于或等于0，建议保留4位小数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">2. 选择字段必须使用下拉选项；“全部”由系统展开，多选组合使用英文逗号（,）分隔</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">否</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">为空时继承日基准量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">3. 考核周期只能单选周或月</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">为空时继承日返利单价</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">4. 同一范围组合的生效日期重叠时阻止导入</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">5. 跨月数据由系统拆分，Excel中无需按月重复填写</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">6. 导入失败数据进入待处理信息池，业务修改后可继续导入</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">为空时按当天星期继承工作日或周日基准量</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">为空时按当天星期继承工作日或周日返利单价</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">产品类型选择项</x:t>
@@ -412,13 +262,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="7">
     <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <x:numFmt numFmtId="177" formatCode="0.0000"/>
+    <x:numFmt numFmtId="200" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="30">
     <x:font>
@@ -1138,7 +989,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="45">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -1239,6 +1090,11 @@
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="49" applyFont="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="50">
     <x:cellStyle name="常规" xfId="0"/>
@@ -1752,37 +1608,37 @@
       <x:c r="H2" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I2" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J2" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K2" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L2" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M2" s="34">
+      <x:c r="I2" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J2" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K2" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L2" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M2" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N2" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O2" s="34">
+      <x:c r="N2" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O2" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P2" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P2" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15">
       <x:c r="A3" s="33">
         <x:v>46280</x:v>
       </x:c>
-      <x:c r="B3" s="35">
-        <x:v>46276</x:v>
+      <x:c r="B3" s="35" t="n">
+        <x:v>46295</x:v>
       </x:c>
       <x:c r="C3" s="36" t="s">
         <x:v>21</x:v>
@@ -1802,29 +1658,29 @@
       <x:c r="H3" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I3">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J3" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K3" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L3" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M3" s="34">
+      <x:c r="I3" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J3" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K3" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L3" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M3" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N3" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O3" s="34">
+      <x:c r="N3" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O3" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P3" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P3" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15">
@@ -1852,29 +1708,29 @@
       <x:c r="H4" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I4" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J4" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K4" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L4" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M4" s="34">
+      <x:c r="I4" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J4" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K4" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L4" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M4" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N4" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O4" s="34">
+      <x:c r="N4" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O4" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P4" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P4" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15">
@@ -1902,29 +1758,29 @@
       <x:c r="H5" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I5">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J5" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K5" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L5" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M5" s="34">
+      <x:c r="I5" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J5" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K5" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L5" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M5" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N5" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O5" s="34">
+      <x:c r="N5" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O5" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P5" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P5" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15">
@@ -1952,29 +1808,29 @@
       <x:c r="H6" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I6" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J6" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K6" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L6" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M6" s="34">
+      <x:c r="I6" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J6" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K6" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L6" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M6" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N6" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O6" s="34">
+      <x:c r="N6" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O6" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P6" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P6" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15">
@@ -2002,29 +1858,29 @@
       <x:c r="H7" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I7">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J7" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K7" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L7" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M7" s="34">
+      <x:c r="I7" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J7" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K7" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L7" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M7" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N7" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O7" s="34">
+      <x:c r="N7" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O7" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P7" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P7" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15">
@@ -2052,29 +1908,29 @@
       <x:c r="H8" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I8" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J8" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K8" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L8" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M8" s="34">
+      <x:c r="I8" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J8" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K8" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L8" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M8" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N8" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O8" s="34">
+      <x:c r="N8" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O8" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P8" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P8" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15">
@@ -2102,29 +1958,29 @@
       <x:c r="H9" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I9">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J9" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K9" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L9" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M9" s="34">
+      <x:c r="I9" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J9" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K9" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L9" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M9" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N9" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O9" s="34">
+      <x:c r="N9" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O9" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P9" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P9" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15">
@@ -2152,29 +2008,29 @@
       <x:c r="H10" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I10" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J10" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K10" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L10" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M10" s="34">
+      <x:c r="I10" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J10" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K10" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L10" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M10" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N10" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O10" s="34">
+      <x:c r="N10" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O10" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P10" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P10" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15">
@@ -2202,29 +2058,29 @@
       <x:c r="H11" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I11">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J11" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K11" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L11" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M11" s="34">
+      <x:c r="I11" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J11" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K11" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L11" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M11" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N11" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O11" s="34">
+      <x:c r="N11" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O11" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P11" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P11" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15">
@@ -2252,29 +2108,29 @@
       <x:c r="H12" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I12" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J12" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K12" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L12" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M12" s="34">
+      <x:c r="I12" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J12" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K12" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L12" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M12" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N12" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O12" s="34">
+      <x:c r="N12" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O12" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P12" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P12" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15">
@@ -2302,29 +2158,29 @@
       <x:c r="H13" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I13">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J13" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K13" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L13" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M13" s="34">
+      <x:c r="I13" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J13" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K13" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L13" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M13" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N13" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O13" s="34">
+      <x:c r="N13" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O13" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P13" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P13" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15">
@@ -2352,29 +2208,29 @@
       <x:c r="H14" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I14" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J14" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K14" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L14" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M14" s="34">
+      <x:c r="I14" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J14" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K14" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L14" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M14" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N14" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O14" s="34">
+      <x:c r="N14" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O14" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P14" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P14" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15">
@@ -2402,29 +2258,29 @@
       <x:c r="H15" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I15">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J15" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K15" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L15" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M15" s="34">
+      <x:c r="I15" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J15" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K15" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L15" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M15" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N15" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O15" s="34">
+      <x:c r="N15" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O15" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P15" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P15" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15">
@@ -2452,29 +2308,29 @@
       <x:c r="H16" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I16" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J16" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K16" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L16" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M16" s="34">
+      <x:c r="I16" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J16" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K16" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L16" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M16" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N16" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O16" s="34">
+      <x:c r="N16" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O16" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P16" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P16" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15">
@@ -2502,29 +2358,29 @@
       <x:c r="H17" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I17">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J17" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K17" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L17" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M17" s="34">
+      <x:c r="I17" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J17" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K17" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L17" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M17" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N17" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O17" s="34">
+      <x:c r="N17" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O17" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P17" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P17" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15">
@@ -2552,29 +2408,29 @@
       <x:c r="H18" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I18" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J18" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K18" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L18" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M18" s="34">
+      <x:c r="I18" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J18" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K18" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L18" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M18" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N18" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O18" s="34">
+      <x:c r="N18" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O18" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P18" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P18" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15">
@@ -2602,29 +2458,29 @@
       <x:c r="H19" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I19">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J19" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K19" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L19" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M19" s="34">
+      <x:c r="I19" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J19" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K19" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L19" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M19" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N19" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O19" s="34">
+      <x:c r="N19" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O19" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P19" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P19" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15">
@@ -2652,29 +2508,29 @@
       <x:c r="H20" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I20" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J20" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K20" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L20" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M20" s="34">
+      <x:c r="I20" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J20" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K20" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L20" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M20" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N20" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O20" s="34">
+      <x:c r="N20" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O20" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P20" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P20" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="15">
@@ -2702,29 +2558,29 @@
       <x:c r="H21" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="I21">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J21" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K21" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="L21" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M21" s="34">
+      <x:c r="I21" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J21" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K21" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="L21" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M21" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N21" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O21" s="34">
+      <x:c r="N21" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O21" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P21" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P21" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="15">
@@ -2752,29 +2608,29 @@
       <x:c r="H22" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I22" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J22" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K22">
+      <x:c r="I22" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J22" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K22" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L22" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M22" s="34">
+      <x:c r="L22" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M22" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N22" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O22" s="34">
+      <x:c r="N22" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O22" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P22" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P22" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="15">
@@ -2802,29 +2658,29 @@
       <x:c r="H23" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I23">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J23" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K23">
+      <x:c r="I23" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J23" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K23" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L23" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M23" s="34">
+      <x:c r="L23" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M23" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N23" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O23" s="34">
+      <x:c r="N23" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O23" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P23" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P23" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="15">
@@ -2852,29 +2708,29 @@
       <x:c r="H24" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I24" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J24" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K24">
+      <x:c r="I24" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J24" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K24" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L24" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M24" s="34">
+      <x:c r="L24" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M24" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N24" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O24" s="34">
+      <x:c r="N24" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O24" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P24" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P24" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15">
@@ -2902,29 +2758,29 @@
       <x:c r="H25" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I25" s="41" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="J25" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K25">
+      <x:c r="I25" s="44" t="n">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J25" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K25" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L25" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M25" s="34">
+      <x:c r="L25" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M25" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N25" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O25" s="34">
+      <x:c r="N25" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O25" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P25" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P25" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="15">
@@ -2952,29 +2808,29 @@
       <x:c r="H26" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I26" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J26" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K26">
+      <x:c r="I26" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J26" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K26" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L26" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M26" s="34">
+      <x:c r="L26" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M26" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N26" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O26" s="34">
+      <x:c r="N26" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O26" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P26" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P26" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="15">
@@ -3002,29 +2858,29 @@
       <x:c r="H27" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I27">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J27" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K27">
+      <x:c r="I27" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J27" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K27" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L27" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M27" s="34">
+      <x:c r="L27" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M27" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N27" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O27" s="34">
+      <x:c r="N27" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O27" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P27" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P27" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="15">
@@ -3052,29 +2908,29 @@
       <x:c r="H28" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I28" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J28" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K28">
+      <x:c r="I28" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J28" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K28" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L28" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M28" s="34">
+      <x:c r="L28" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M28" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N28" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O28" s="34">
+      <x:c r="N28" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O28" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P28" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P28" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="15">
@@ -3102,29 +2958,29 @@
       <x:c r="H29" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I29" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J29" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K29">
+      <x:c r="I29" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J29" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K29" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L29" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M29" s="34">
+      <x:c r="L29" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M29" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N29" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O29" s="34">
+      <x:c r="N29" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O29" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P29" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P29" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="15">
@@ -3152,29 +3008,29 @@
       <x:c r="H30" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I30">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J30" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K30">
+      <x:c r="I30" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J30" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K30" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L30" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M30" s="34">
+      <x:c r="L30" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M30" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N30" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O30" s="34">
+      <x:c r="N30" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O30" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P30" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P30" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="15">
@@ -3202,29 +3058,29 @@
       <x:c r="H31" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I31" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J31" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K31">
+      <x:c r="I31" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J31" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K31" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L31" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M31" s="34">
+      <x:c r="L31" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M31" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N31" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O31" s="34">
+      <x:c r="N31" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O31" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P31" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P31" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="15">
@@ -3252,29 +3108,29 @@
       <x:c r="H32" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I32" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J32" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K32">
+      <x:c r="I32" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J32" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K32" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L32" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M32" s="34">
+      <x:c r="L32" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M32" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N32" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O32" s="34">
+      <x:c r="N32" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O32" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P32" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P32" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="15">
@@ -3302,29 +3158,29 @@
       <x:c r="H33" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I33">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J33" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K33">
+      <x:c r="I33" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J33" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K33" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L33" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M33" s="34">
+      <x:c r="L33" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M33" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N33" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O33" s="34">
+      <x:c r="N33" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O33" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P33" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P33" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="15">
@@ -3352,29 +3208,29 @@
       <x:c r="H34" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I34" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J34" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K34">
+      <x:c r="I34" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J34" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K34" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L34" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M34" s="34">
+      <x:c r="L34" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M34" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N34" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O34" s="34">
+      <x:c r="N34" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O34" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P34" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P34" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="15">
@@ -3385,7 +3241,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C35" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D35" s="37" t="s">
         <x:v>22</x:v>
@@ -3402,29 +3258,29 @@
       <x:c r="H35" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I35" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J35" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K35">
+      <x:c r="I35" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J35" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K35" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L35" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M35" s="34">
+      <x:c r="L35" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M35" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N35" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O35" s="34">
+      <x:c r="N35" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O35" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P35" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P35" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="15">
@@ -3435,7 +3291,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C36" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D36" s="37" t="s">
         <x:v>24</x:v>
@@ -3452,29 +3308,29 @@
       <x:c r="H36" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I36">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J36" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K36">
+      <x:c r="I36" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J36" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K36" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L36" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M36" s="34">
+      <x:c r="L36" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M36" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N36" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O36" s="34">
+      <x:c r="N36" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O36" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P36" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P36" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="15">
@@ -3485,7 +3341,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C37" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D37" s="37" t="s">
         <x:v>25</x:v>
@@ -3502,29 +3358,29 @@
       <x:c r="H37" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I37" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J37" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K37">
+      <x:c r="I37" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J37" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K37" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L37" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M37" s="34">
+      <x:c r="L37" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M37" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N37" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O37" s="34">
+      <x:c r="N37" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O37" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P37" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P37" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="15">
@@ -3535,7 +3391,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C38" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D38" s="37" t="s">
         <x:v>26</x:v>
@@ -3552,29 +3408,29 @@
       <x:c r="H38" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I38" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J38" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K38">
+      <x:c r="I38" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J38" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K38" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L38" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M38" s="34">
+      <x:c r="L38" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M38" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N38" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O38" s="34">
+      <x:c r="N38" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O38" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P38" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P38" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="15">
@@ -3585,7 +3441,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C39" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D39" s="37" t="s">
         <x:v>27</x:v>
@@ -3602,29 +3458,29 @@
       <x:c r="H39" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I39">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J39" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K39">
+      <x:c r="I39" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J39" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K39" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L39" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M39" s="34">
+      <x:c r="L39" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M39" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N39" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O39" s="34">
+      <x:c r="N39" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O39" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P39" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P39" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="15">
@@ -3635,7 +3491,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C40" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D40" s="37" t="s">
         <x:v>28</x:v>
@@ -3652,29 +3508,29 @@
       <x:c r="H40" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I40" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J40" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K40">
+      <x:c r="I40" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J40" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K40" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L40" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M40" s="34">
+      <x:c r="L40" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M40" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N40" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O40" s="34">
+      <x:c r="N40" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O40" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P40" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P40" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="15">
@@ -3685,7 +3541,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C41" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D41" s="37" t="s">
         <x:v>29</x:v>
@@ -3702,29 +3558,29 @@
       <x:c r="H41" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I41" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J41" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K41">
+      <x:c r="I41" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J41" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K41" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L41" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M41" s="34">
+      <x:c r="L41" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M41" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N41" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O41" s="34">
+      <x:c r="N41" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O41" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P41" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P41" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="15">
@@ -3735,7 +3591,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C42" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D42" s="37" t="s">
         <x:v>30</x:v>
@@ -3752,29 +3608,29 @@
       <x:c r="H42" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I42">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J42" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K42">
+      <x:c r="I42" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J42" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K42" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L42" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M42" s="34">
+      <x:c r="L42" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M42" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N42" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O42" s="34">
+      <x:c r="N42" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O42" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P42" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P42" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="15">
@@ -3785,7 +3641,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C43" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D43" s="37" t="s">
         <x:v>31</x:v>
@@ -3802,29 +3658,29 @@
       <x:c r="H43" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I43" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J43" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K43">
+      <x:c r="I43" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J43" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K43" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L43" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M43" s="34">
+      <x:c r="L43" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M43" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N43" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O43" s="34">
+      <x:c r="N43" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O43" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P43" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P43" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="15">
@@ -3835,7 +3691,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C44" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D44" s="37" t="s">
         <x:v>32</x:v>
@@ -3852,29 +3708,29 @@
       <x:c r="H44" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I44" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J44" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K44">
+      <x:c r="I44" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J44" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K44" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L44" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M44" s="34">
+      <x:c r="L44" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M44" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N44" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O44" s="34">
+      <x:c r="N44" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O44" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P44" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P44" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="15">
@@ -3885,7 +3741,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C45" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D45" s="37" t="s">
         <x:v>33</x:v>
@@ -3902,29 +3758,29 @@
       <x:c r="H45" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I45">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J45" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K45">
+      <x:c r="I45" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J45" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K45" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L45" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M45" s="34">
+      <x:c r="L45" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M45" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N45" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O45" s="34">
+      <x:c r="N45" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O45" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P45" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P45" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="15">
@@ -3935,7 +3791,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C46" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D46" s="37" t="s">
         <x:v>34</x:v>
@@ -3952,29 +3808,29 @@
       <x:c r="H46" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I46" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J46" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K46">
+      <x:c r="I46" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J46" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K46" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L46" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M46" s="34">
+      <x:c r="L46" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M46" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N46" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O46" s="34">
+      <x:c r="N46" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O46" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P46" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P46" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="15">
@@ -3985,7 +3841,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C47" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D47" s="37" t="s">
         <x:v>35</x:v>
@@ -4002,29 +3858,29 @@
       <x:c r="H47" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I47" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J47" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K47">
+      <x:c r="I47" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J47" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K47" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L47" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M47" s="34">
+      <x:c r="L47" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M47" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N47" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O47" s="34">
+      <x:c r="N47" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O47" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P47" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P47" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="15">
@@ -4035,7 +3891,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C48" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D48" s="37" t="s">
         <x:v>36</x:v>
@@ -4052,29 +3908,29 @@
       <x:c r="H48" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I48">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J48" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K48">
+      <x:c r="I48" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J48" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K48" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L48" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M48" s="34">
+      <x:c r="L48" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M48" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N48" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O48" s="34">
+      <x:c r="N48" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O48" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P48" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P48" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="15">
@@ -4085,7 +3941,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C49" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D49" s="37" t="s">
         <x:v>38</x:v>
@@ -4102,29 +3958,29 @@
       <x:c r="H49" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I49" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J49" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K49">
+      <x:c r="I49" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J49" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K49" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L49" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M49" s="34">
+      <x:c r="L49" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M49" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N49" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O49" s="34">
+      <x:c r="N49" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O49" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P49" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P49" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="15">
@@ -4135,7 +3991,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C50" s="36" t="s">
-        <x:v>43</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D50" s="37" t="s">
         <x:v>39</x:v>
@@ -4152,29 +4008,29 @@
       <x:c r="H50" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I50" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J50" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K50">
+      <x:c r="I50" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J50" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K50" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L50" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M50" s="34">
+      <x:c r="L50" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M50" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N50" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O50" s="34">
+      <x:c r="N50" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O50" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P50" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P50" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="15">
@@ -4185,7 +4041,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C51" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D51" s="37" t="s">
         <x:v>22</x:v>
@@ -4202,29 +4058,29 @@
       <x:c r="H51" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I51">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J51" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K51">
+      <x:c r="I51" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J51" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K51" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L51" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M51" s="34">
+      <x:c r="L51" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M51" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N51" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O51" s="34">
+      <x:c r="N51" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O51" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P51" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P51" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="15">
@@ -4235,7 +4091,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C52" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D52" s="37" t="s">
         <x:v>24</x:v>
@@ -4252,29 +4108,29 @@
       <x:c r="H52" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I52" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J52" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K52">
+      <x:c r="I52" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J52" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K52" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L52" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M52" s="34">
+      <x:c r="L52" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M52" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N52" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O52" s="34">
+      <x:c r="N52" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O52" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P52" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P52" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="15">
@@ -4285,7 +4141,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C53" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D53" s="37" t="s">
         <x:v>25</x:v>
@@ -4302,29 +4158,29 @@
       <x:c r="H53" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I53" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J53" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K53">
+      <x:c r="I53" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J53" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K53" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L53" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M53" s="34">
+      <x:c r="L53" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M53" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N53" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O53" s="34">
+      <x:c r="N53" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O53" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P53" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P53" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="15">
@@ -4335,7 +4191,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C54" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D54" s="37" t="s">
         <x:v>26</x:v>
@@ -4352,29 +4208,29 @@
       <x:c r="H54" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I54">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J54" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K54">
+      <x:c r="I54" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J54" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K54" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L54" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M54" s="34">
+      <x:c r="L54" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M54" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N54" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O54" s="34">
+      <x:c r="N54" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O54" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P54" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P54" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="15">
@@ -4385,7 +4241,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C55" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D55" s="37" t="s">
         <x:v>27</x:v>
@@ -4402,29 +4258,29 @@
       <x:c r="H55" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I55" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J55" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K55">
+      <x:c r="I55" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J55" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K55" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L55" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M55" s="34">
+      <x:c r="L55" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M55" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N55" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O55" s="34">
+      <x:c r="N55" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O55" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P55" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P55" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="15">
@@ -4435,7 +4291,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C56" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D56" s="37" t="s">
         <x:v>28</x:v>
@@ -4452,29 +4308,29 @@
       <x:c r="H56" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I56" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J56" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K56">
+      <x:c r="I56" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J56" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K56" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L56" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M56" s="34">
+      <x:c r="L56" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M56" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N56" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O56" s="34">
+      <x:c r="N56" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O56" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P56" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P56" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="15">
@@ -4485,7 +4341,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C57" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D57" s="37" t="s">
         <x:v>29</x:v>
@@ -4502,29 +4358,29 @@
       <x:c r="H57" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I57">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J57" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K57">
+      <x:c r="I57" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J57" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K57" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L57" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M57" s="34">
+      <x:c r="L57" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M57" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N57" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O57" s="34">
+      <x:c r="N57" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O57" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P57" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P57" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="15">
@@ -4535,7 +4391,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C58" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D58" s="37" t="s">
         <x:v>30</x:v>
@@ -4552,29 +4408,29 @@
       <x:c r="H58" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I58" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J58" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K58">
+      <x:c r="I58" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J58" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K58" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L58" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M58" s="34">
+      <x:c r="L58" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M58" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N58" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O58" s="34">
+      <x:c r="N58" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O58" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P58" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P58" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="15">
@@ -4585,7 +4441,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C59" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D59" s="37" t="s">
         <x:v>31</x:v>
@@ -4602,29 +4458,29 @@
       <x:c r="H59" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I59" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J59" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K59">
+      <x:c r="I59" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J59" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K59" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L59" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M59" s="34">
+      <x:c r="L59" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M59" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N59" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O59" s="34">
+      <x:c r="N59" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O59" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P59" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P59" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="15">
@@ -4635,7 +4491,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C60" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D60" s="37" t="s">
         <x:v>27</x:v>
@@ -4652,29 +4508,29 @@
       <x:c r="H60" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I60" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J60" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K60">
+      <x:c r="I60" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J60" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K60" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L60" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M60" s="34">
+      <x:c r="L60" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M60" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N60" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O60" s="34">
+      <x:c r="N60" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O60" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P60" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P60" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="15">
@@ -4685,7 +4541,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C61" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D61" s="37" t="s">
         <x:v>28</x:v>
@@ -4702,29 +4558,29 @@
       <x:c r="H61" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I61" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J61" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K61">
+      <x:c r="I61" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J61" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K61" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L61" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M61" s="34">
+      <x:c r="L61" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M61" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N61" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O61" s="34">
+      <x:c r="N61" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O61" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P61" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P61" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="15">
@@ -4735,7 +4591,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C62" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D62" s="37" t="s">
         <x:v>29</x:v>
@@ -4752,29 +4608,29 @@
       <x:c r="H62" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I62">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J62" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K62">
+      <x:c r="I62" s="43">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J62" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K62" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L62" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M62" s="34">
+      <x:c r="L62" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M62" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N62" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O62" s="34">
+      <x:c r="N62" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O62" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P62" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P62" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="15">
@@ -4785,7 +4641,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C63" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D63" s="37" t="s">
         <x:v>30</x:v>
@@ -4802,29 +4658,29 @@
       <x:c r="H63" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I63" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J63" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K63">
+      <x:c r="I63" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J63" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K63" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L63" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M63" s="34">
+      <x:c r="L63" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M63" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N63" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O63" s="34">
+      <x:c r="N63" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O63" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P63" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P63" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="15">
@@ -4835,7 +4691,7 @@
         <x:v>46295</x:v>
       </x:c>
       <x:c r="C64" s="36" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D64" s="37" t="s">
         <x:v>31</x:v>
@@ -4852,29 +4708,29 @@
       <x:c r="H64" s="41" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="I64" s="34">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="J64" s="34">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="K64">
+      <x:c r="I64" s="42">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="J64" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="K64" s="43">
         <x:v>650</x:v>
       </x:c>
-      <x:c r="L64" s="34">
-        <x:v>0.012</x:v>
-      </x:c>
-      <x:c r="M64" s="34">
+      <x:c r="L64" s="42" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="M64" s="42">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="N64" s="34">
-        <x:v>0.016</x:v>
-      </x:c>
-      <x:c r="O64" s="34">
+      <x:c r="N64" s="42" t="n">
+        <x:v>0.02</x:v>
+      </x:c>
+      <x:c r="O64" s="42">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="P64" s="34">
-        <x:v>0.022</x:v>
+      <x:c r="P64" s="42" t="n">
+        <x:v>0.02</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4939,17 +4795,33 @@
     <x:col min="9" max="9" width="36" customWidth="1"/>
   </x:cols>
   <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1"/>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
+      <x:c r="H1"/>
+      <x:c r="I1"/>
+    </x:row>
     <x:row r="2" ht="30" customHeight="1">
-      <x:c r="A2" s="11" t="s">
-        <x:v>45</x:v>
+      <x:c r="A2" s="11" t="str">
+        <x:v>网点返利政策导入填写说明</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
       <x:c r="C2" s="11"/>
       <x:c r="D2" s="11"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
+      <x:c r="G2"/>
+      <x:c r="H2"/>
+      <x:c r="I2"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="12" t="s">
-        <x:v>46</x:v>
+      <x:c r="A3" s="12" t="str">
+        <x:v>日期字段使用日期校验；产品类型、货物类型和公斤段使用下拉列表，可选择全部、单个或预组合的多个值；考核周期只能单选。</x:v>
       </x:c>
       <x:c r="B3" s="12"/>
       <x:c r="C3" s="12"/>
@@ -4960,363 +4832,403 @@
       <x:c r="H3" s="12"/>
       <x:c r="I3" s="12"/>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
+      <x:c r="G4"/>
+      <x:c r="H4"/>
+      <x:c r="I4"/>
+    </x:row>
     <x:row r="5" ht="28" customHeight="1">
-      <x:c r="A5" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="F5" s="13" t="s">
-        <x:v>51</x:v>
+      <x:c r="A5" s="1" t="str">
+        <x:v>字段名称</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="str">
+        <x:v>是否必填</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="str">
+        <x:v>填写格式</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="str">
+        <x:v>填写规则</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5" s="13" t="str">
+        <x:v>系统拆分规则示例</x:v>
       </x:c>
       <x:c r="G5" s="13"/>
       <x:c r="H5" s="13"/>
       <x:c r="I5" s="13"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="14" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B6" s="15" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D6" s="16" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F6" s="17" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G6" s="17" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H6" s="17" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I6" s="17" t="s">
-        <x:v>58</x:v>
+      <x:c r="A6" s="14" t="str">
+        <x:v>生效开始日期</x:v>
+      </x:c>
+      <x:c r="B6" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="str">
+        <x:v>日期选择</x:v>
+      </x:c>
+      <x:c r="D6" s="16" t="str">
+        <x:v>选择或输入政策生效起始日期，不得晚于结束日期</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6" s="17" t="str">
+        <x:v>输入项目</x:v>
+      </x:c>
+      <x:c r="G6" s="17" t="str">
+        <x:v>示例</x:v>
+      </x:c>
+      <x:c r="H6" s="17" t="str">
+        <x:v>数量</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str">
+        <x:v>说明</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B7" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C7" s="19" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D7" s="20" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F7" s="21" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G7" s="22" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="H7" s="22">
+      <x:c r="A7" s="18" t="str">
+        <x:v>生效结束日期</x:v>
+      </x:c>
+      <x:c r="B7" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C7" s="19" t="str">
+        <x:v>日期选择</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>选择或输入政策生效结束日期；允许跨月并由系统按自然月拆分</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7" s="21" t="str">
+        <x:v>日期范围</x:v>
+      </x:c>
+      <x:c r="G7" s="22" t="str">
+        <x:v>2026-09-15 至 2026-10-31</x:v>
+      </x:c>
+      <x:c r="H7" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I7" s="23" t="s">
-        <x:v>62</x:v>
+      <x:c r="I7" s="23" t="str">
+        <x:v>跨2个自然月</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="s">
+      <x:c r="A8" s="18" t="str">
+        <x:v>寄件网点</x:v>
+      </x:c>
+      <x:c r="B8" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C8" s="19" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>填写系统中的标准网点名称</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8" s="24" t="str">
+        <x:v>产品类型</x:v>
+      </x:c>
+      <x:c r="G8" s="25" t="str">
+        <x:v>融汇达,精准零担</x:v>
+      </x:c>
+      <x:c r="H8" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B8" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C8" s="19" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D8" s="20" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F8" s="24" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="25" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H8" s="25">
+      <x:c r="I8" s="26" t="str">
+        <x:v>选择2个产品类型</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="18" t="str">
+        <x:v>目的流向</x:v>
+      </x:c>
+      <x:c r="B9" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C9" s="19" t="str">
+        <x:v>文本</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>填写分拨或营运区名称；营运区覆盖导入时快照内的分拨</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9" s="24" t="str">
+        <x:v>货物类型</x:v>
+      </x:c>
+      <x:c r="G9" s="25" t="str">
+        <x:v>轻泡,重泡,重货</x:v>
+      </x:c>
+      <x:c r="H9" s="25" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I8" s="26" t="s">
-        <x:v>65</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="18" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="19" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D9" s="20" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="F9" s="24" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G9" s="25" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H9" s="25">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I9" s="26" t="s">
-        <x:v>67</x:v>
+      <x:c r="I9" s="26" t="str">
+        <x:v>选择2个货物类型</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="18" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B10" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C10" s="19" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D10" s="20" t="s">
-        <x:v>69</x:v>
-      </x:c>
+      <x:c r="A10" s="18" t="str">
+        <x:v>产品类型</x:v>
+      </x:c>
+      <x:c r="B10" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C10" s="19" t="str">
+        <x:v>列表选择</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>下拉可选择全部、单个或预组合的多个产品类型</x:v>
+      </x:c>
+      <x:c r="E10"/>
       <x:c r="F10" s="24" t="str">
         <x:v>公斤段</x:v>
       </x:c>
-      <x:c r="G10" s="25" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H10" s="25">
+      <x:c r="G10" s="25" t="str">
+        <x:v>0kg-100kg,100kg-300kg,300kg-800kg,800kg-1500kg</x:v>
+      </x:c>
+      <x:c r="H10" s="25" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I10" s="26" t="s">
-        <x:v>70</x:v>
+      <x:c r="I10" s="26" t="str">
+        <x:v>选择3个公斤段</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="18" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B11" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C11" s="19" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D11" s="20" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="F11" s="27" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G11" s="28" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="H11" s="28">
+      <x:c r="A11" s="18" t="str">
+        <x:v>货物类型</x:v>
+      </x:c>
+      <x:c r="B11" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C11" s="19" t="str">
+        <x:v>列表选择</x:v>
+      </x:c>
+      <x:c r="D11" s="20" t="str">
+        <x:v>下拉可选择全部、单个或预组合的多个货物类型：轻泡、重泡、重货</x:v>
+      </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11" s="27" t="str">
+        <x:v>拆分结果</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="str">
+        <x:v>2 × 2 × 2 × 3</x:v>
+      </x:c>
+      <x:c r="H11" s="28" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="I11" s="29" t="s">
-        <x:v>74</x:v>
+      <x:c r="I11" s="29" t="str">
+        <x:v>导入系统后形成24条月度配置</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="18" t="str">
         <x:v>公斤段</x:v>
       </x:c>
-      <x:c r="B12" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C12" s="19" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D12" s="20" t="s">
-        <x:v>75</x:v>
-      </x:c>
+      <x:c r="B12" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C12" s="19" t="str">
+        <x:v>列表选择</x:v>
+      </x:c>
+      <x:c r="D12" s="20" t="str">
+        <x:v>仅可选择0kg-100kg、100kg-300kg、300kg-800kg、800kg-1500kg；支持全部、单选和预组合多选</x:v>
+      </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="18" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B13" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C13" s="19" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D13" s="20" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="F13" s="30" t="s">
-        <x:v>78</x:v>
+      <x:c r="A13" s="18" t="str">
+        <x:v>考核周期</x:v>
+      </x:c>
+      <x:c r="B13" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C13" s="19" t="str">
+        <x:v>单选列表</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="str">
+        <x:v>只能单选周或月</x:v>
+      </x:c>
+      <x:c r="E13"/>
+      <x:c r="F13" s="30" t="str">
+        <x:v>导入校验</x:v>
       </x:c>
       <x:c r="G13" s="30"/>
       <x:c r="H13" s="30"/>
       <x:c r="I13" s="30"/>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="18" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B14" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C14" s="19" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D14" s="20" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F14" s="31" t="s">
-        <x:v>81</x:v>
+      <x:c r="A14" s="18" t="str">
+        <x:v>日基准量</x:v>
+      </x:c>
+      <x:c r="B14" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C14" s="19" t="str">
+        <x:v>数值（kg）</x:v>
+      </x:c>
+      <x:c r="D14" s="20" t="str">
+        <x:v>大于或等于0</x:v>
+      </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14" s="31" t="str">
+        <x:v>1. 日期、网点、流向和必填字段不能为空</x:v>
       </x:c>
       <x:c r="G14" s="31"/>
       <x:c r="H14" s="31"/>
       <x:c r="I14" s="31"/>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="18" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B15" s="19" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C15" s="19" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D15" s="20" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="F15" s="31" t="s">
-        <x:v>84</x:v>
+      <x:c r="A15" s="18" t="str">
+        <x:v>日返利单价</x:v>
+      </x:c>
+      <x:c r="B15" s="19" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="C15" s="19" t="str">
+        <x:v>数值（元/kg）</x:v>
+      </x:c>
+      <x:c r="D15" s="20" t="str">
+        <x:v>大于或等于0，最多保留2位小数</x:v>
+      </x:c>
+      <x:c r="E15"/>
+      <x:c r="F15" s="31" t="str">
+        <x:v>2. 选择字段必须使用下拉选项；“全部”由系统展开，多选组合使用英文逗号（,）分隔</x:v>
       </x:c>
       <x:c r="G15" s="31"/>
       <x:c r="H15" s="31"/>
       <x:c r="I15" s="31"/>
     </x:row>
     <x:row r="16" ht="26" customHeight="1">
-      <x:c r="A16" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B16" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D16" s="7" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F16" s="31" t="s">
-        <x:v>87</x:v>
+      <x:c r="A16" s="5" t="str">
+        <x:v>工作日基准量</x:v>
+      </x:c>
+      <x:c r="B16" s="6" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="str">
+        <x:v>数值（kg）</x:v>
+      </x:c>
+      <x:c r="D16" s="7" t="str">
+        <x:v>为空时继承日基准量</x:v>
+      </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16" s="31" t="str">
+        <x:v>3. 考核周期只能单选周或月</x:v>
       </x:c>
       <x:c r="G16" s="31"/>
       <x:c r="H16" s="31"/>
       <x:c r="I16" s="31"/>
     </x:row>
     <x:row r="17" ht="26" customHeight="1">
-      <x:c r="A17" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B17" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C17" s="6" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D17" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F17" s="31" t="s">
-        <x:v>89</x:v>
+      <x:c r="A17" s="5" t="str">
+        <x:v>工作日返利单价</x:v>
+      </x:c>
+      <x:c r="B17" s="6" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="C17" s="6" t="str">
+        <x:v>数值（元/kg）</x:v>
+      </x:c>
+      <x:c r="D17" s="7" t="str">
+        <x:v>为空时继承日返利单价</x:v>
+      </x:c>
+      <x:c r="E17"/>
+      <x:c r="F17" s="31" t="str">
+        <x:v>4. 同一政策适用范围的重叠生效日期，导入时作为替换候选并由用户确认；Excel文件内部的后续重复行进入信息池。</x:v>
       </x:c>
       <x:c r="G17" s="31"/>
       <x:c r="H17" s="31"/>
       <x:c r="I17" s="31"/>
     </x:row>
     <x:row r="18" ht="26" customHeight="1">
-      <x:c r="A18" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B18" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C18" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D18" s="7" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F18" s="31" t="s">
-        <x:v>90</x:v>
+      <x:c r="A18" s="5" t="str">
+        <x:v>周日基准量</x:v>
+      </x:c>
+      <x:c r="B18" s="6" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="C18" s="6" t="str">
+        <x:v>数值（kg）</x:v>
+      </x:c>
+      <x:c r="D18" s="7" t="str">
+        <x:v>为空时继承日基准量</x:v>
+      </x:c>
+      <x:c r="E18"/>
+      <x:c r="F18" s="31" t="str">
+        <x:v>5. 跨月数据由系统拆分，Excel中无需按月重复填写</x:v>
       </x:c>
       <x:c r="G18" s="31"/>
       <x:c r="H18" s="31"/>
       <x:c r="I18" s="31"/>
     </x:row>
     <x:row r="19" ht="26" customHeight="1">
-      <x:c r="A19" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B19" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C19" s="6" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D19" s="7" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F19" s="31" t="s">
-        <x:v>91</x:v>
+      <x:c r="A19" s="5" t="str">
+        <x:v>周日返利单价</x:v>
+      </x:c>
+      <x:c r="B19" s="6" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="C19" s="6" t="str">
+        <x:v>数值（元/kg）</x:v>
+      </x:c>
+      <x:c r="D19" s="7" t="str">
+        <x:v>为空时继承日返利单价</x:v>
+      </x:c>
+      <x:c r="E19"/>
+      <x:c r="F19" s="31" t="str">
+        <x:v>6. 导入失败数据进入待处理信息池，业务修改后可继续导入</x:v>
       </x:c>
       <x:c r="G19" s="31"/>
       <x:c r="H19" s="31"/>
       <x:c r="I19" s="31"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B20" s="6" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C20" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D20" s="7" t="s">
-        <x:v>92</x:v>
-      </x:c>
+      <x:c r="A20" s="5" t="str">
+        <x:v>节假日基准量</x:v>
+      </x:c>
+      <x:c r="B20" s="6" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="C20" s="6" t="str">
+        <x:v>数值（kg）</x:v>
+      </x:c>
+      <x:c r="D20" s="7" t="str">
+        <x:v>为空时按当天星期继承工作日或周日基准量</x:v>
+      </x:c>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+      <x:c r="G20"/>
+      <x:c r="H20"/>
+      <x:c r="I20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="8" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B21" s="9" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="C21" s="9" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D21" s="10" t="s">
-        <x:v>93</x:v>
-      </x:c>
+      <x:c r="A21" s="8" t="str">
+        <x:v>节假日返利单价</x:v>
+      </x:c>
+      <x:c r="B21" s="9" t="str">
+        <x:v>否</x:v>
+      </x:c>
+      <x:c r="C21" s="9" t="str">
+        <x:v>数值（元/kg）</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="str">
+        <x:v>为空时按当天星期继承工作日或周日返利单价</x:v>
+      </x:c>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+      <x:c r="G21"/>
+      <x:c r="H21"/>
+      <x:c r="I21"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -5348,47 +5260,47 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C1" s="1" t="str">
         <x:v>公斤段选择项</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>98</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>99</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="5" t="s">
-        <x:v>100</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="C3" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D3" s="6" t="s">
         <x:v>41</x:v>
@@ -5397,39 +5309,39 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D4" s="6"/>
       <x:c r="E4" s="7"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="5" t="s">
-        <x:v>105</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D5" s="6"/>
       <x:c r="E5" s="7"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="5" t="s">
-        <x:v>108</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>110</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D6" s="6"/>
       <x:c r="E6" s="7"/>
@@ -5439,111 +5351,111 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>111</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D7" s="6"/>
       <x:c r="E7" s="7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="5" t="s">
-        <x:v>113</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D8" s="6"/>
       <x:c r="E8" s="7"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B9" s="6"/>
       <x:c r="C9" s="6" t="s">
-        <x:v>117</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D9" s="6"/>
       <x:c r="E9" s="7"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="5" t="s">
-        <x:v>118</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B10" s="6"/>
       <x:c r="C10" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D10" s="6"/>
       <x:c r="E10" s="7"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B11" s="6"/>
       <x:c r="C11" s="6" t="s">
-        <x:v>121</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D11" s="6"/>
       <x:c r="E11" s="7"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="5" t="s">
-        <x:v>122</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B12" s="6"/>
       <x:c r="C12" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D12" s="6"/>
       <x:c r="E12" s="7"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="5" t="s">
-        <x:v>124</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B13" s="6"/>
       <x:c r="C13" s="6" t="s">
-        <x:v>125</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D13" s="6"/>
       <x:c r="E13" s="7"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="5" t="s">
-        <x:v>126</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B14" s="6"/>
       <x:c r="C14" s="6" t="s">
-        <x:v>127</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D14" s="6"/>
       <x:c r="E14" s="7"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="5" t="s">
-        <x:v>128</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B15" s="6"/>
       <x:c r="C15" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D15" s="6"/>
       <x:c r="E15" s="7"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="5" t="s">
-        <x:v>130</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B16" s="6"/>
       <x:c r="C16" s="6" t="s">
-        <x:v>131</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D16" s="6"/>
       <x:c r="E16" s="7"/>
